--- a/sports_forms/012_fitness_calculator--sports_forms.xlsx
+++ b/sports_forms/012_fitness_calculator--sports_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'sedentary_(lightly_active)',_'value':_'sedentary_(lightly_active)'}</t>
+          <t>sedentary_(lightly_active)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Sedentary (Lightly active)', 'value': 'Sedentary (Lightly active)'}</t>
+          <t>Sedentary (Lightly active)</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'lightly_active',_'value':_'lightly_active'}</t>
+          <t>lightly_active</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Lightly Active', 'value': 'Lightly Active'}</t>
+          <t>Lightly Active</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'moderately_active',_'value':_'moderately_active'}</t>
+          <t>moderately_active</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Moderately Active', 'value': 'Moderately Active'}</t>
+          <t>Moderately Active</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'highly_active',_'value':_'highly_active'}</t>
+          <t>highly_active</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Highly Active', 'value': 'Highly Active'}</t>
+          <t>Highly Active</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'very_active',_'value':_'very_active'}</t>
+          <t>very_active</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Very Active', 'value': 'Very Active'}</t>
+          <t>Very Active</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'sedentary_(lightly_active)',_'value':_'sedentary_(lightly_active)'}</t>
+          <t>sedentary_(lightly_active)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Sedentary (Lightly active)', 'value': 'Sedentary (Lightly active)'}</t>
+          <t>Sedentary (Lightly active)</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'lightly_active',_'value':_'lightly_active'}</t>
+          <t>lightly_active</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Lightly Active', 'value': 'Lightly Active'}</t>
+          <t>Lightly Active</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'moderately_active',_'value':_'moderately_active'}</t>
+          <t>moderately_active</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Moderately Active', 'value': 'Moderately Active'}</t>
+          <t>Moderately Active</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'highly_active',_'value':_'highly_active'}</t>
+          <t>highly_active</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Highly Active', 'value': 'Highly Active'}</t>
+          <t>Highly Active</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'very_active',_'value':_'very_active'}</t>
+          <t>very_active</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Very Active', 'value': 'Very Active'}</t>
+          <t>Very Active</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'mmhg',_'value':_'mmhg'}</t>
+          <t>mmhg</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'mmHg', 'value': 'mmHg'}</t>
+          <t>mmHg</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'mmmhg',_'value':_'mmmhg'}</t>
+          <t>mmmhg</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'mmmHg', 'value': 'mmmHg'}</t>
+          <t>mmmHg</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'kpa',_'value':_'kpa'}</t>
+          <t>kpa</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'kPa', 'value': 'kPa'}</t>
+          <t>kPa</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'mmhg',_'value':_'mmhg'}</t>
+          <t>mmhg</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'mmHg', 'value': 'mmHg'}</t>
+          <t>mmHg</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'mmmhg',_'value':_'mmmhg'}</t>
+          <t>mmmhg</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'mmmHg', 'value': 'mmmHg'}</t>
+          <t>mmmHg</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'kpa',_'value':_'kpa'}</t>
+          <t>kpa</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'kPa', 'value': 'kPa'}</t>
+          <t>kPa</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'mmhg',_'value':_'mmhg'}</t>
+          <t>mmhg</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'mmHg', 'value': 'mmHg'}</t>
+          <t>mmHg</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'mmmhg',_'value':_'mmmhg'}</t>
+          <t>mmmhg</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'mmmHg', 'value': 'mmmHg'}</t>
+          <t>mmmHg</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'kpa',_'value':_'kpa'}</t>
+          <t>kpa</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'kPa', 'value': 'kPa'}</t>
+          <t>kPa</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'mmhg',_'value':_'mmhg'}</t>
+          <t>mmhg</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'mmHg', 'value': 'mmHg'}</t>
+          <t>mmHg</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'mmmhg',_'value':_'mmmhg'}</t>
+          <t>mmmhg</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'mmmHg', 'value': 'mmmHg'}</t>
+          <t>mmmHg</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'kpa',_'value':_'kpa'}</t>
+          <t>kpa</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'kPa', 'value': 'kPa'}</t>
+          <t>kPa</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'c',_'value':_'c'}</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'C', 'value': 'C'}</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'f',_'value':_'f'}</t>
+          <t>f</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'F', 'value': 'F'}</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'k',_'value':_'k'}</t>
+          <t>k</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'K', 'value': 'K'}</t>
+          <t>K</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'lightly',_'value':_'lightly'}</t>
+          <t>lightly</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Lightly', 'value': 'Lightly'}</t>
+          <t>Lightly</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'moderately',_'value':_'moderately'}</t>
+          <t>moderately</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Moderately', 'value': 'Moderately'}</t>
+          <t>Moderately</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'highly',_'value':_'highly'}</t>
+          <t>highly</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Highly', 'value': 'Highly'}</t>
+          <t>Highly</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'rarely',_'value':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Rarely', 'value': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'occasionally',_'value':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Occasionally', 'value': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'frequently',_'value':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Frequently', 'value': 'Frequently'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'often',_'value':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Often', 'value': 'Often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
